--- a/load_testing/test_reports/travix_baseline_load_report.xlsx
+++ b/load_testing/test_reports/travix_baseline_load_report.xlsx
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>17/8/2026, 8:53:55 am</t>
+    <t>18/8/2026, 9:20:18 am</t>
   </si>
   <si>
     <t>Virtual Users (VU):</t>
@@ -44,7 +44,7 @@
     <t>Benchmark Status:</t>
   </si>
   <si>
-    <t>WARNING - HIGH LATENCY/ERRORS</t>
+    <t>PASS - EXCELLENT PERFORMANCE</t>
   </si>
   <si>
     <t>Concurrent VUs</t>
@@ -65,10 +65,10 @@
     <t>Benchmark Status</t>
   </si>
   <si>
-    <t>889.5 req/sec</t>
-  </si>
-  <si>
-    <t>57.46%</t>
+    <t>1377.9 req/sec</t>
+  </si>
+  <si>
+    <t>0%</t>
   </si>
   <si>
     <t>FAST &amp; STABLE</t>
@@ -98,19 +98,19 @@
     <t>API Latency</t>
   </si>
   <si>
-    <t>1 ms</t>
-  </si>
-  <si>
-    <t>60 ms</t>
-  </si>
-  <si>
-    <t>338 ms</t>
-  </si>
-  <si>
-    <t>183 ms</t>
-  </si>
-  <si>
-    <t>241 ms</t>
+    <t>0 ms</t>
+  </si>
+  <si>
+    <t>11 ms</t>
+  </si>
+  <si>
+    <t>205 ms</t>
+  </si>
+  <si>
+    <t>26 ms</t>
+  </si>
+  <si>
+    <t>49 ms</t>
   </si>
   <si>
     <t>Endpoint Name</t>
@@ -745,7 +745,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="4">
-        <v>53504</v>
+        <v>82751</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -862,7 +862,7 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>16051</v>
+        <v>24825</v>
       </c>
       <c r="F2" t="s">
         <v>44</v>
@@ -885,7 +885,7 @@
         <v>48</v>
       </c>
       <c r="E3">
-        <v>13376</v>
+        <v>20688</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -908,7 +908,7 @@
         <v>52</v>
       </c>
       <c r="E4">
-        <v>10701</v>
+        <v>16550</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
@@ -931,7 +931,7 @@
         <v>55</v>
       </c>
       <c r="E5">
-        <v>8026</v>
+        <v>12413</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
@@ -954,7 +954,7 @@
         <v>58</v>
       </c>
       <c r="E6">
-        <v>5350</v>
+        <v>8275</v>
       </c>
       <c r="F6" t="s">
         <v>44</v>

--- a/load_testing/test_reports/travix_baseline_load_report.xlsx
+++ b/load_testing/test_reports/travix_baseline_load_report.xlsx
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>8/18/2026, 5:45:31 AM</t>
+    <t>8/18/2026, 5:56:29 AM</t>
   </si>
   <si>
     <t>Virtual Users (VU):</t>
@@ -65,7 +65,7 @@
     <t>Benchmark Status</t>
   </si>
   <si>
-    <t>1870.6 req/sec</t>
+    <t>1854.5 req/sec</t>
   </si>
   <si>
     <t>0%</t>
@@ -104,13 +104,13 @@
     <t>3 ms</t>
   </si>
   <si>
-    <t>177 ms</t>
-  </si>
-  <si>
-    <t>8 ms</t>
-  </si>
-  <si>
-    <t>17 ms</t>
+    <t>202 ms</t>
+  </si>
+  <si>
+    <t>9 ms</t>
+  </si>
+  <si>
+    <t>18 ms</t>
   </si>
   <si>
     <t>Endpoint Name</t>
@@ -745,7 +745,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="4">
-        <v>112334</v>
+        <v>111365</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -862,7 +862,7 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>33700</v>
+        <v>33410</v>
       </c>
       <c r="F2" t="s">
         <v>44</v>
@@ -885,7 +885,7 @@
         <v>48</v>
       </c>
       <c r="E3">
-        <v>28084</v>
+        <v>27841</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -908,7 +908,7 @@
         <v>52</v>
       </c>
       <c r="E4">
-        <v>22467</v>
+        <v>22273</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
@@ -931,7 +931,7 @@
         <v>55</v>
       </c>
       <c r="E5">
-        <v>16850</v>
+        <v>16705</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
@@ -954,7 +954,7 @@
         <v>58</v>
       </c>
       <c r="E6">
-        <v>11233</v>
+        <v>11137</v>
       </c>
       <c r="F6" t="s">
         <v>44</v>

--- a/load_testing/test_reports/travix_baseline_load_report.xlsx
+++ b/load_testing/test_reports/travix_baseline_load_report.xlsx
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>8/18/2026, 5:56:29 AM</t>
+    <t>8/18/2026, 6:21:31 AM</t>
   </si>
   <si>
     <t>Virtual Users (VU):</t>
@@ -65,7 +65,7 @@
     <t>Benchmark Status</t>
   </si>
   <si>
-    <t>1854.5 req/sec</t>
+    <t>1880.5 req/sec</t>
   </si>
   <si>
     <t>0%</t>
@@ -104,13 +104,13 @@
     <t>3 ms</t>
   </si>
   <si>
-    <t>202 ms</t>
-  </si>
-  <si>
-    <t>9 ms</t>
-  </si>
-  <si>
-    <t>18 ms</t>
+    <t>173 ms</t>
+  </si>
+  <si>
+    <t>7 ms</t>
+  </si>
+  <si>
+    <t>14 ms</t>
   </si>
   <si>
     <t>Endpoint Name</t>
@@ -745,7 +745,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="4">
-        <v>111365</v>
+        <v>112919</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -862,7 +862,7 @@
         <v>43</v>
       </c>
       <c r="E2">
-        <v>33410</v>
+        <v>33876</v>
       </c>
       <c r="F2" t="s">
         <v>44</v>
@@ -885,7 +885,7 @@
         <v>48</v>
       </c>
       <c r="E3">
-        <v>27841</v>
+        <v>28230</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -908,7 +908,7 @@
         <v>52</v>
       </c>
       <c r="E4">
-        <v>22273</v>
+        <v>22584</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
@@ -931,7 +931,7 @@
         <v>55</v>
       </c>
       <c r="E5">
-        <v>16705</v>
+        <v>16938</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
@@ -954,7 +954,7 @@
         <v>58</v>
       </c>
       <c r="E6">
-        <v>11137</v>
+        <v>11292</v>
       </c>
       <c r="F6" t="s">
         <v>44</v>
